--- a/Configs/GameConfig/Datas/fg/#CombatComponent-作战组件.xlsx
+++ b/Configs/GameConfig/Datas/fg/#CombatComponent-作战组件.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB14"/>
+  <dimension ref="A1:AI19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -557,6 +557,41 @@
           <t>icon</t>
         </is>
       </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>fieldPlace</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>droneMode</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>echoCount</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>echoDelay</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>echoRatio</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>thorns</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>thornsReach</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -699,6 +734,41 @@
           <t>string</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -743,7 +813,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>基础伤害:&gt;0 时用本值(新组件);0 = 沿用 Demo 规则(连射器 / 切割束按电路编译伤害,重炮 55)</t>
+          <t>基础伤害:&gt;0 时用本值(新组件);0 = 沿用 Demo 规则(连射器 / 切割束按电路编译伤害,重炮 55);反伤功能组件 = 反伤固定值</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -839,6 +909,41 @@
       <c r="AB3" t="inlineStr">
         <is>
           <t>图标ID</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>布区落点:hit=目标脚下,self=自己脚下(布区·脉冲,要贴近才出手)</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>无人机方式:follow=伴飞母机,post=定点(哨戒桩:插在身前不动,射程=droneLeash)</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>组件自带回波次数(拆解钳:夹住后持续拆解)</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>组件自带回波间隔(游戏秒)</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>组件自带回波每次伤害 = 基础伤害 × 本值</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>反伤比例(功能组件尖刺外装:被近身即时攻击时,攻击者吃 damage 列的固定值 + 这一击伤害 × 本值)</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>反伤触及(米,另加双方半径):攻击者在这个距离内才算近战</t>
         </is>
       </c>
     </row>
@@ -949,6 +1054,31 @@
           <t>icon_comp_gun</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>hit</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>follow</t>
+        </is>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
@@ -1057,6 +1187,31 @@
           <t>icon_comp_beam</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>hit</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>follow</t>
+        </is>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
@@ -1165,6 +1320,31 @@
           <t>icon_comp_cannon</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>hit</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>follow</t>
+        </is>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
@@ -1273,6 +1453,31 @@
           <t>icon_comp_repairbeam</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>hit</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>follow</t>
+        </is>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
@@ -1381,6 +1586,31 @@
           <t>icon_func_dash</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>hit</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>follow</t>
+        </is>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
@@ -1489,6 +1719,31 @@
           <t>icon_func_marker</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>hit</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>follow</t>
+        </is>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
@@ -1597,6 +1852,31 @@
           <t>icon_comp_ram</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>hit</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>follow</t>
+        </is>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
@@ -1705,6 +1985,31 @@
           <t>icon_comp_shovel</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>hit</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>follow</t>
+        </is>
+      </c>
+      <c r="AE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
@@ -1813,6 +2118,31 @@
           <t>icon_comp_dronebay</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>hit</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>follow</t>
+        </is>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
@@ -1921,6 +2251,31 @@
           <t>icon_comp_corona</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>hit</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>follow</t>
+        </is>
+      </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr"/>
@@ -2028,6 +2383,696 @@
         <is>
           <t>icon_comp_sprayer</t>
         </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>hit</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>follow</t>
+        </is>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>comp_orbit</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>melee</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>component.subtype.melee_orbit</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>component.comp_orbit.name</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>component.comp_orbit.desc</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>org_orbitcilia</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>8</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>2</v>
+      </c>
+      <c r="N15" t="n">
+        <v>180</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>base</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>icon_comp_orbit</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>hit</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>follow</t>
+        </is>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>comp_sentry</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>summon</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>component.subtype.drone_post</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>component.comp_sentry.name</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>component.comp_sentry.desc</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>org_mycelium</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>9</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>6</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2</v>
+      </c>
+      <c r="S16" t="n">
+        <v>14</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
+      </c>
+      <c r="V16" t="n">
+        <v>7</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>base</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>icon_comp_sentry</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>hit</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>comp_pulser</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>field</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>component.subtype.field_pulse</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>component.comp_pulser.name</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>component.comp_pulser.desc</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>org_wave</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>6</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>base</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>icon_comp_pulser</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>self</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>follow</t>
+        </is>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>comp_claw</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>melee</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>component.subtype.melee_grip</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>component.comp_claw.name</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>component.comp_claw.desc</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>org_phago</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>10</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>2</v>
+      </c>
+      <c r="N18" t="n">
+        <v>20</v>
+      </c>
+      <c r="O18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>base</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>icon_comp_claw</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>hit</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>follow</t>
+        </is>
+      </c>
+      <c r="AE18" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>func_spikes</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>function</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>component.subtype.melee_thorns</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>component.func_spikes.name</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>component.func_spikes.desc</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>org_spine</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>4</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>base</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>icon_func_spikes</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>hit</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>follow</t>
+        </is>
+      </c>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/GameConfig/Datas/fg/#CombatComponent-作战组件.xlsx
+++ b/Configs/GameConfig/Datas/fg/#CombatComponent-作战组件.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI19"/>
+  <dimension ref="A1:AO19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -592,6 +592,36 @@
           <t>thornsReach</t>
         </is>
       </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>flight</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>flightSpeed</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>flightRadius</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>flightLifeScale</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>flightLob</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>kinetic</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -769,6 +799,36 @@
           <t>float</t>
         </is>
       </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -944,6 +1004,36 @@
       <c r="AI3" t="inlineStr">
         <is>
           <t>反伤触及(米,另加双方半径):攻击者在这个距离内才算近战</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>根载荷实体化:yes=允许(程序需要飞行时武器置 SpawnFlight、当场结算改为生成飞行弹体),no=不实体化(格斗/力场/布区/功能组件)</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>实体化弹速(米/秒;yes 行必须 &gt;0,缺值表校验与 FgChannelAdmissionSelfCheck 失败,运行时不退回即时命中;no 行填 0)</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>实体化弹体半径(米;yes 行必须 &gt;0)</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>实体化弹体寿命 = 射程(无人机为牵引绳) ÷ 弹速 × 本值(yes 行必须 &gt;0)</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>1 = 可抛射(grm.mod.lob 生效);0 = 直线(光束:曲射只留落点扬尘)</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>动能系数(FG19B §6.3)</t>
         </is>
       </c>
     </row>
@@ -1079,6 +1169,26 @@
       <c r="AI4" t="n">
         <v>0</v>
       </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AK4" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
@@ -1212,6 +1322,26 @@
       <c r="AI5" t="n">
         <v>0</v>
       </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AK5" t="n">
+        <v>45</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
@@ -1345,6 +1475,26 @@
       <c r="AI6" t="n">
         <v>0</v>
       </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AK6" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
@@ -1478,6 +1628,26 @@
       <c r="AI7" t="n">
         <v>0</v>
       </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AK7" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
@@ -1611,6 +1781,26 @@
       <c r="AI8" t="n">
         <v>0</v>
       </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
@@ -1744,6 +1934,26 @@
       <c r="AI9" t="n">
         <v>0</v>
       </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
@@ -1877,6 +2087,26 @@
       <c r="AI10" t="n">
         <v>0</v>
       </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>2.2</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
@@ -2010,6 +2240,26 @@
       <c r="AI11" t="n">
         <v>0</v>
       </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>2.2</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
@@ -2143,6 +2393,26 @@
       <c r="AI12" t="n">
         <v>0</v>
       </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AK12" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
@@ -2276,6 +2546,26 @@
       <c r="AI13" t="n">
         <v>0</v>
       </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr"/>
@@ -2409,6 +2699,26 @@
       <c r="AI14" t="n">
         <v>0</v>
       </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0.3</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr"/>
@@ -2542,6 +2852,26 @@
       <c r="AI15" t="n">
         <v>0</v>
       </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>2.2</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr"/>
@@ -2675,6 +3005,26 @@
       <c r="AI16" t="n">
         <v>0</v>
       </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AK16" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr"/>
@@ -2808,6 +3158,26 @@
       <c r="AI17" t="n">
         <v>0</v>
       </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0.3</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr"/>
@@ -2941,6 +3311,26 @@
       <c r="AI18" t="n">
         <v>0</v>
       </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>2.2</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
@@ -3073,6 +3463,26 @@
       </c>
       <c r="AI19" t="n">
         <v>1.5</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
